--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.8136495315734</v>
+        <v>9.719718048880678</v>
       </c>
       <c r="D2" t="n">
-        <v>61.98567564075228</v>
+        <v>10.07267229162225</v>
       </c>
       <c r="E2" t="n">
-        <v>13.29429342086502</v>
+        <v>2.160322680890566</v>
       </c>
       <c r="F2" t="n">
-        <v>14.03943374896741</v>
+        <v>2.281407984207203</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.34185170381133</v>
+        <v>9.155550901869342</v>
       </c>
       <c r="D3" t="n">
-        <v>58.43078360604201</v>
+        <v>9.495002335981827</v>
       </c>
       <c r="E3" t="n">
-        <v>13.29429342086502</v>
+        <v>2.160322680890566</v>
       </c>
       <c r="F3" t="n">
-        <v>14.03943374896741</v>
+        <v>2.281407984207203</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.51136658540747</v>
+        <v>5.120597070128714</v>
       </c>
       <c r="D4" t="n">
-        <v>30.99520059091855</v>
+        <v>5.036720096024265</v>
       </c>
       <c r="E4" t="n">
-        <v>13.29429342086502</v>
+        <v>2.160322680890566</v>
       </c>
       <c r="F4" t="n">
-        <v>14.03943374896741</v>
+        <v>2.281407984207203</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.52952102680023</v>
+        <v>4.473547166855036</v>
       </c>
       <c r="D5" t="n">
-        <v>25.35570627251111</v>
+        <v>4.120302269283056</v>
       </c>
       <c r="E5" t="n">
-        <v>13.29429342086502</v>
+        <v>2.160322680890566</v>
       </c>
       <c r="F5" t="n">
-        <v>14.03943374896741</v>
+        <v>2.281407984207203</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.07000399779591</v>
+        <v>6.673875649641835</v>
       </c>
       <c r="D6" t="n">
-        <v>38.97294956220146</v>
+        <v>6.333104303857738</v>
       </c>
       <c r="E6" t="n">
-        <v>13.29429342086502</v>
+        <v>2.160322680890566</v>
       </c>
       <c r="F6" t="n">
-        <v>14.03943374896741</v>
+        <v>2.281407984207203</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.22125812549606</v>
+        <v>7.67345444539311</v>
       </c>
       <c r="D7" t="n">
-        <v>45.29128085428152</v>
+        <v>7.359833138820748</v>
       </c>
       <c r="E7" t="n">
-        <v>13.29429342086502</v>
+        <v>2.160322680890566</v>
       </c>
       <c r="F7" t="n">
-        <v>14.03943374896741</v>
+        <v>2.281407984207203</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>54.0597447496473</v>
+        <v>8.784708521817686</v>
       </c>
       <c r="D8" t="n">
-        <v>51.91246254994464</v>
+        <v>8.435775164366003</v>
       </c>
       <c r="E8" t="n">
-        <v>13.29429342086502</v>
+        <v>2.160322680890566</v>
       </c>
       <c r="F8" t="n">
-        <v>14.03943374896741</v>
+        <v>2.281407984207203</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.01237846660634</v>
+        <v>3.577011500823529</v>
       </c>
       <c r="D9" t="n">
-        <v>22.22264132410121</v>
+        <v>3.611179215166448</v>
       </c>
       <c r="E9" t="n">
-        <v>13.29429342086502</v>
+        <v>2.160322680890566</v>
       </c>
       <c r="F9" t="n">
-        <v>14.03943374896741</v>
+        <v>2.281407984207203</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
